--- a/Backend/dekiru/src/main/resources/templates/Template_Import_SinhVien.xlsx
+++ b/Backend/dekiru/src/main/resources/templates/Template_Import_SinhVien.xlsx
@@ -1,120 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backend\dekiru\src\main\resources\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E3D68C6-78B7-4E1D-9E00-A2F9813D5D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BE191E2-CCD7-4521-8AEB-D115C5E91ACF}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Họ và tên</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mã sinh viên</t>
-  </si>
-  <si>
-    <t>Mã lớp hành chính</t>
-  </si>
-  <si>
-    <t>Phạm Trọng D</t>
-  </si>
-  <si>
-    <t>phamtrongd@example.com</t>
-  </si>
-  <si>
-    <t>SV2023001</t>
-  </si>
-  <si>
-    <t>IT01</t>
-  </si>
-  <si>
-    <t>Hoàng Thị E</t>
-  </si>
-  <si>
-    <t>hoangthie@example.com</t>
-  </si>
-  <si>
-    <t>SV2023002</t>
-  </si>
-  <si>
-    <t>Vũ Văn F</t>
-  </si>
-  <si>
-    <t>vuvanf@example.com</t>
-  </si>
-  <si>
-    <t>SV2023003</t>
-  </si>
-  <si>
-    <t>KT02</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF1F1F1F"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F1F1F"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,11 +59,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -147,139 +73,176 @@
   <dxfs count="6">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <b val="1"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FF1F1F1F"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{946BCC79-018B-4AF6-B69A-07647ECAEEC8}" name="Table1" displayName="Table1" ref="A1:D4" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:D4" xr:uid="{946BCC79-018B-4AF6-B69A-07647ECAEEC8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D4" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:D4"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F6088E88-A897-4FB4-9E62-ED8322330FB3}" name="Họ và tên" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{11154500-D2E1-483A-B8F4-1E016FD44930}" name="Email" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E7A01B91-D373-48B4-A735-B5B1D1FED73B}" name="Mã sinh viên" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{46234F1F-4A69-4367-A576-27AC41016F59}" name="Mã lớp hành chính" dataDxfId="2"/>
+    <tableColumn id="1" name="Họ và tên" dataDxfId="5"/>
+    <tableColumn id="2" name="Email" dataDxfId="4"/>
+    <tableColumn id="3" name="Mã sinh viên" dataDxfId="3"/>
+    <tableColumn id="4" name="Mã lớp hành chính" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -601,76 +564,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F628FF8-11B9-4EB7-BCC7-830B06A4851D}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col width="12.85546875" customWidth="1" min="1" max="1"/>
+    <col width="39.140625" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="21.85546875" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Họ và tên</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mã sinh viên</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mã lớp hành chính</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Số điện thoại</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Giới tính</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ngày sinh</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Nơi sinh</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="57" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
+    <row r="2" ht="57" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Phạm Trọng D</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>phamtrongd@example.com</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SV2023001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IT01</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
+    <row r="3" ht="57" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Hoàng Thị E</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>hoangthie@example.com</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SV2023002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>IT01</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
+    <row r="4" ht="42.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Vũ Văn F</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>vuvanf@example.com</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SV2023003</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>KT02</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>